--- a/artfynd/A 55518-2025 artfynd.xlsx
+++ b/artfynd/A 55518-2025 artfynd.xlsx
@@ -675,41 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74137648</v>
+        <v>74624322</v>
       </c>
       <c r="B2" t="n">
-        <v>106131</v>
+        <v>107611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>225197</v>
+        <v>1897</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Äkta ljungsnärja</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cuscuta epithymum var. epithymum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Melampyrum cristatum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vigelsbo 300 m VNV, Sm</t>
+          <t>2 Vigelsbo 400 m NV, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583167</v>
+        <v>583166</v>
       </c>
       <c r="R2" t="n">
-        <v>6401025</v>
+        <v>6401125</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -736,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1981-01-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1981-12-31</t>
+          <t>1987-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G0h 2202. SOM: Cuscuta epithymum var. epithymum. LEG: Björn Widén</t>
+          <t>Smålands flora 2007: KOO: 7G0h 2302. SOM: Melampyrum cristatum. LEG: Björn Widén</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Betesmark, parasit på teveronika</t>
+          <t>Vid bergbas, sydvänd</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74551464</v>
+        <v>74977107</v>
       </c>
       <c r="B3" t="n">
-        <v>101746</v>
+        <v>111398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221223</v>
+        <v>219716</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -857,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G0h 2302. SOM: Lathyrus niger. LEG: Björn Widén</t>
+          <t>Smålands flora 2007: KOO: 7G0h 2302. SOM: Selinum carvifolia. LEG: Björn Widén</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sydbrant</t>
+          <t>Gölkant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -893,45 +897,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74624322</v>
+        <v>74765629</v>
       </c>
       <c r="B4" t="n">
-        <v>107087</v>
+        <v>99156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1897</v>
+        <v>219875</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2 Vigelsbo 400 m NV, Sm</t>
+          <t>15 Vigelsbo 300 m VNV, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583166</v>
+        <v>583167</v>
       </c>
       <c r="R4" t="n">
-        <v>6401125</v>
+        <v>6401025</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -968,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G0h 2302. SOM: Melampyrum cristatum. LEG: Björn Widén</t>
+          <t>Smålands flora 2007: KOO: 7G0h 2202. SOM: Platanthera chlorantha. LEG: Björn Widén</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Vid bergbas, sydvänd</t>
+          <t>Igenväxande betesmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,45 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74765629</v>
+        <v>74551464</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>102224</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>221223</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>15 Vigelsbo 300 m VNV, Sm</t>
+          <t>2 Vigelsbo 400 m NV, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583167</v>
+        <v>583166</v>
       </c>
       <c r="R5" t="n">
-        <v>6401025</v>
+        <v>6401125</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1079,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G0h 2202. SOM: Platanthera chlorantha. LEG: Björn Widén</t>
+          <t>Smålands flora 2007: KOO: 7G0h 2302. SOM: Lathyrus niger. LEG: Björn Widén</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Igenväxande betesmark</t>
+          <t>Sydbrant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1115,45 +1119,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74977107</v>
+        <v>74137648</v>
       </c>
       <c r="B6" t="n">
-        <v>110806</v>
+        <v>106649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219716</v>
+        <v>225197</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Äkta ljungsnärja</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) L.</t>
-        </is>
-      </c>
+          <t>Cuscuta epithymum var. epithymum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2 Vigelsbo 400 m NV, Sm</t>
+          <t>Vigelsbo 300 m VNV, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583166</v>
+        <v>583167</v>
       </c>
       <c r="R6" t="n">
-        <v>6401125</v>
+        <v>6401025</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1180,17 +1180,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1987-12-31</t>
+          <t>1981-12-31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G0h 2302. SOM: Selinum carvifolia. LEG: Björn Widén</t>
+          <t>Smålands flora 2007: KOO: 7G0h 2202. SOM: Cuscuta epithymum var. epithymum. LEG: Björn Widén</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Gölkant</t>
+          <t>Betesmark, parasit på teveronika</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
